--- a/jogos_2024-12-09.xlsx
+++ b/jogos_2024-12-09.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Mladost Novi Sad</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.4</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="AD7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['43', '90+3', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['27', '39']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45635.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost Novi Sad</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="M10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.75</v>
       </c>
-      <c r="N10" t="n">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X10" t="n">
         <v>3.3</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.18</v>
-      </c>
       <c r="Y10" t="n">
-        <v>2.85</v>
+        <v>2.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['43', '90+3', '90+4']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '39']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45635.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kallithea</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
         <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="X11" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['23', '52']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['56', '63', '69', '90+8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45635.52083333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,19 +1933,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Kallithea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.22</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['23', '52']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56', '63', '69', '90+8']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45635.52083333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,28 +2346,28 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="O15" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
         <v>2.63</v>
@@ -2376,25 +2376,25 @@
         <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.65</v>
+        <v>3.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AC15" t="n">
         <v>1.62</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['18', '28', '34', '44']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ15" t="n">
         <v>2.05</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['2', '30', '85', '89']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45635.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Şanlıurfaspor</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="P17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['12', '69']</t>
+          <t>['10', '17', '37', '40', '70', '90']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45635.58333333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,28 +2733,28 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3.1</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
       </c>
       <c r="T18" t="n">
         <v>2.63</v>
@@ -2763,25 +2763,25 @@
         <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X18" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.06</v>
+        <v>2.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC18" t="n">
         <v>1.62</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['18', '28', '34', '44']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,13 +2800,13 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AJ18" t="n">
         <v>2.05</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,16 +2836,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GOŠK Gabela</t>
+          <t>Şanlıurfaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.15</v>
+        <v>1.87</v>
       </c>
       <c r="M19" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>2.55</v>
       </c>
       <c r="P19" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>4.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="X19" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.27</v>
+        <v>1.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.43</v>
+        <v>3.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['27', '46', '75', '88']</t>
+          <t>['12', '69']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.14</v>
+        <v>1.58</v>
       </c>
       <c r="AJ19" t="n">
-        <v>6.5</v>
+        <v>2.62</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45635.58333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
         <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X20" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['2', '30', '85', '89']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45635.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>GOŠK Gabela</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.6</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>12</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.38</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['10', '17', '37', '40', '70', '90']</t>
+          <t>['27', '46', '75', '88']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>3.35</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45635.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3642,37 +3642,37 @@
         <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P25" t="n">
         <v>2.2</v>
       </c>
       <c r="Q25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.75</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Y25" t="n">
         <v>1.85</v>
@@ -3681,38 +3681,38 @@
         <v>1.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.38</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['82', '90+4']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AI25" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45635.625</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3771,37 +3771,37 @@
         <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O26" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Y26" t="n">
         <v>1.85</v>
@@ -3810,16 +3810,16 @@
         <v>1.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3828,20 +3828,20 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82', '90+4']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45635.625</v>
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -4158,71 +4158,71 @@
         <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q29" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z29" t="n">
         <v>2.4</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X29" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['12', '90+7']</t>
+          <t>['17', '78']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '85', '88']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" t="n">
         <v>2.38</v>
@@ -4384,19 +4384,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -4416,71 +4416,71 @@
         <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O31" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q31" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['17', '78']</t>
+          <t>['12', '90+7']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['52', '85', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI31" t="n">
         <v>2.38</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="M33" t="n">
         <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.5</v>
       </c>
-      <c r="S33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X33" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['70', '83']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['20', '53']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.44</v>
       </c>
-      <c r="AH33" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI33" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45635.6875</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
         <v>2</v>
       </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="M35" t="n">
         <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['20', '53']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['70', '83']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['90+5']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45635.6875</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
         <v>2</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.85</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="AA36" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['6', '70']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['90', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45635.69791666666</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,109 +5158,109 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['90', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH37" t="n">
         <v>2</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X37" t="n">
+      <c r="AI37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>2.75</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['47']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['6', '70']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45635.69791666666</v>
@@ -5277,32 +5277,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>2</v>
       </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="O38" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="T38" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="U38" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W38" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="X38" t="n">
-        <v>4.75</v>
+        <v>2.35</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>4.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['28', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['22', '69']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45635.70833333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="O39" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P39" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="U39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.2</v>
       </c>
-      <c r="V39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y39" t="n">
         <v>1.6</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA39" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['54', '72']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45635.70833333334</v>
@@ -5535,32 +5535,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N40" t="n">
         <v>2.1</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>3.75</v>
       </c>
-      <c r="O40" t="n">
-        <v>3</v>
-      </c>
       <c r="P40" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="U40" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.87</v>
+        <v>2.45</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '84']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['22', '69']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45635.70833333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>3.6</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['54', '72']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45635.70833333334</v>
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M44" t="n">
         <v>3.1</v>
       </c>
-      <c r="M44" t="n">
-        <v>3</v>
-      </c>
       <c r="N44" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC44" t="n">
         <v>2.5</v>
       </c>
-      <c r="O44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2</v>
-      </c>
       <c r="AD44" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['17', '88']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['42', '61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45635.80208333334</v>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P45" t="n">
         <v>1.95</v>
       </c>
-      <c r="M45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['17', '88']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>['42', '61']</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ45" t="n">
         <v>1.83</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>['7']</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>3.2</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45635.80208333334</v>
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huracán</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>6</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X46" t="n">
         <v>2.35</v>
       </c>
-      <c r="M46" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="N46" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T46" t="n">
-        <v>4</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y46" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>7.15</v>
+        <v>5.31</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['14', '75']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45635.89583333334</v>
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>Huracán</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="N47" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="P47" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S47" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T47" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V47" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="W47" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="X47" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>5.31</v>
+        <v>7.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['14', '75']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45635.89583333334</v>
